--- a/KatalonData/RADTestData/MFLNLessThanFiveError.xlsx
+++ b/KatalonData/RADTestData/MFLNLessThanFiveError.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>Result</t>
   </si>
@@ -75,6 +75,33 @@
   </si>
   <si>
     <t>Sat Jun 20 23:21:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:04:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:04:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 21:11:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 21:11:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 21:23:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 21:23:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 23:01:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 23:02:05 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -451,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
@@ -481,11 +508,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
+      <c r="B2" t="s" s="1">
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -498,11 +525,11 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
+      <c r="B3" t="s" s="1">
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
